--- a/results/by_outcome/full_results_education_observed_MI.xlsx
+++ b/results/by_outcome/full_results_education_observed_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.562829559322632</v>
+        <v>0.581854661607804</v>
       </c>
       <c r="I2" t="n">
-        <v>0.181182979478295</v>
+        <v>0.198269688504221</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.437221397807387</v>
+        <v>0.418198027688481</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.574429563149919</v>
+        <v>0.600307577493303</v>
       </c>
       <c r="G3" t="n">
-        <v>0.204399312173213</v>
+        <v>0.226424691997017</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.637314387588559</v>
+        <v>0.6372569072896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.362776158086459</v>
+        <v>0.362833654974204</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00009054567502</v>
+        <v>1.0000905622638</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.362743313229904</v>
+        <v>0.362800798845769</v>
       </c>
       <c r="K4" t="n">
-        <v>0.204380806345658</v>
+        <v>0.22640418829331</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0115989535773228</v>
+        <v>0.0184512449259772</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0744780845774824</v>
+        <v>0.0553972288427121</v>
       </c>
       <c r="N4" t="n">
-        <v>0.215979759922981</v>
+        <v>0.244855433219287</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.362743313229904</v>
+        <v>0.362800798845769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.331478779327946</v>
+        <v>0.332249961018475</v>
       </c>
       <c r="E2" t="n">
-        <v>0.394007847131863</v>
+        <v>0.393351636673063</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000179248785642801</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000795536794946436</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.215979759922981</v>
+        <v>0.244855433219287</v>
       </c>
       <c r="D3" t="n">
-        <v>0.186519911844896</v>
+        <v>0.216381604777069</v>
       </c>
       <c r="E3" t="n">
-        <v>0.245439608001067</v>
+        <v>0.273329261661506</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00000000000000000000000000000000000000000000198477489471125</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000125017730541088</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.437221397807387</v>
+        <v>0.418198027688481</v>
       </c>
       <c r="D4" t="n">
-        <v>0.407382877948978</v>
+        <v>0.388565074698803</v>
       </c>
       <c r="E4" t="n">
-        <v>0.467059917665795</v>
+        <v>0.44783098067816</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000186233541285595</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000203467652812311</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.221241637884405</v>
+        <v>0.173342594469194</v>
       </c>
       <c r="D5" t="n">
-        <v>0.201987873590051</v>
+        <v>0.1560848464279</v>
       </c>
       <c r="E5" t="n">
-        <v>0.24049540217876</v>
+        <v>0.190600342510488</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000542767791162366</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000560084218178785</v>
       </c>
     </row>
   </sheetData>

--- a/results/by_outcome/full_results_education_observed_MI.xlsx
+++ b/results/by_outcome/full_results_education_observed_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.581854661607804</v>
+        <v>0.589993232443389</v>
       </c>
       <c r="I2" t="n">
-        <v>0.198269688504221</v>
+        <v>0.187881397506515</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.418198027688481</v>
+        <v>0.410053757062274</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.600307577493303</v>
+        <v>0.609489261635018</v>
       </c>
       <c r="G3" t="n">
-        <v>0.226424691997017</v>
+        <v>0.215196763079111</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6372569072896</v>
+        <v>0.650143321088707</v>
       </c>
       <c r="D4" t="n">
-        <v>0.362833654974204</v>
+        <v>0.349936329468187</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0000905622638</v>
+        <v>1.00007965055689</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.362800798845769</v>
+        <v>0.349908458991995</v>
       </c>
       <c r="K4" t="n">
-        <v>0.22640418829331</v>
+        <v>0.215179623757746</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0184512449259772</v>
+        <v>0.0194944764664887</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0553972288427121</v>
+        <v>0.0601452980702789</v>
       </c>
       <c r="N4" t="n">
-        <v>0.244855433219287</v>
+        <v>0.234674100224234</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.362800798845769</v>
+        <v>0.349908458991995</v>
       </c>
       <c r="D2" t="n">
-        <v>0.332249961018475</v>
+        <v>0.31968896342866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.393351636673063</v>
+        <v>0.38012795455533</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000795536794946436</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000514839685242371</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.244855433219287</v>
+        <v>0.234674100224234</v>
       </c>
       <c r="D3" t="n">
-        <v>0.216381604777069</v>
+        <v>0.207088633368288</v>
       </c>
       <c r="E3" t="n">
-        <v>0.273329261661506</v>
+        <v>0.26225956708018</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000125017730541088</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000258401106651559</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.418198027688481</v>
+        <v>0.410053757062274</v>
       </c>
       <c r="D4" t="n">
-        <v>0.388565074698803</v>
+        <v>0.382034639022279</v>
       </c>
       <c r="E4" t="n">
-        <v>0.44783098067816</v>
+        <v>0.438072875102269</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000203467652812311</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000433247860122595</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.173342594469194</v>
+        <v>0.17537965683804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1560848464279</v>
+        <v>0.159526833316565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.190600342510488</v>
+        <v>0.191232480359515</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000560084218178785</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000190270339843799</v>
       </c>
     </row>
   </sheetData>
